--- a/ds_v1.xlsx
+++ b/ds_v1.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cumhuriyetedutr-my.sharepoint.com/personal/yasingormez_cumhuriyet_edu_tr/Documents/Makale Çalışmaları/2024 - 06 - 19 - Effect of socio-economic Kubra/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P1657\OneDrive - SİVAS CUMHURİYET ÜNİVERSİTESİ\Makale Çalışmaları\2024 - 06 - 19 - Effect of socio-economic Kubra\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{D540C428-B95C-4034-8966-700CF5FBFB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2F400F5-DCD4-4D2D-94E8-F9446FF023B7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Form Yanıtları 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Form Answers" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Form Yanıtları 1'!$A$1:$AR$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Form Answers'!$A$1:$AR$186</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,9 +23,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="87">
-  <si>
-    <t>Zaman damgası</t>
-  </si>
   <si>
     <t>Gender</t>
   </si>
@@ -318,11 +314,14 @@
     <t>It is necessary to know about English speaking
 cultures in order to learn to speak English</t>
   </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
@@ -611,7 +610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -637,136 +636,136 @@
   <sheetData>
     <row r="1" spans="1:44" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="13.2" x14ac:dyDescent="0.25">
@@ -777,34 +776,34 @@
         <v>2.75</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M2" s="1">
         <v>4</v>
@@ -911,34 +910,34 @@
         <v>3.44</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M3" s="1">
         <v>5</v>
@@ -1045,34 +1044,34 @@
         <v>2.8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M4" s="1">
         <v>5</v>
@@ -1179,34 +1178,34 @@
         <v>3.14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M5" s="1">
         <v>5</v>
@@ -1313,34 +1312,34 @@
         <v>3.24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M6" s="1">
         <v>4</v>
@@ -1447,34 +1446,34 @@
         <v>2.8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M7" s="1">
         <v>5</v>
@@ -1581,34 +1580,34 @@
         <v>2.85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1">
         <v>3</v>
@@ -1715,34 +1714,34 @@
         <v>3.14</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M9" s="1">
         <v>4</v>
@@ -1849,34 +1848,34 @@
         <v>2.98</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M10" s="1">
         <v>5</v>
@@ -1983,34 +1982,34 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M11" s="1">
         <v>5</v>
@@ -2117,34 +2116,34 @@
         <v>3.1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M12" s="1">
         <v>5</v>
@@ -2251,34 +2250,34 @@
         <v>3.34</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M13" s="1">
         <v>5</v>
@@ -2385,34 +2384,34 @@
         <v>3.42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M14" s="1">
         <v>3</v>
@@ -2519,34 +2518,34 @@
         <v>3.25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M15" s="1">
         <v>4</v>
@@ -2653,34 +2652,34 @@
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M16" s="1">
         <v>5</v>
@@ -2787,34 +2786,34 @@
         <v>2.88</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M17" s="1">
         <v>4</v>
@@ -2921,34 +2920,34 @@
         <v>3.3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M18" s="1">
         <v>4</v>
@@ -3055,34 +3054,34 @@
         <v>2.76</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M19" s="1">
         <v>5</v>
@@ -3189,34 +3188,34 @@
         <v>2.77</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M20" s="1">
         <v>3</v>
@@ -3323,34 +3322,34 @@
         <v>2.7</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J21" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M21" s="1">
         <v>5</v>
@@ -3457,34 +3456,34 @@
         <v>2.78</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M22" s="1">
         <v>3</v>
@@ -3591,34 +3590,34 @@
         <v>3.4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M23" s="1">
         <v>4</v>
@@ -3725,34 +3724,34 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M24" s="1">
         <v>4</v>
@@ -3859,34 +3858,34 @@
         <v>3.15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M25" s="1">
         <v>3</v>
@@ -3993,34 +3992,34 @@
         <v>3.17</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M26" s="1">
         <v>3</v>
@@ -4127,34 +4126,34 @@
         <v>3.2</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M27" s="1">
         <v>4</v>
@@ -4261,34 +4260,34 @@
         <v>3.02</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M28" s="1">
         <v>5</v>
@@ -4395,34 +4394,34 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J29" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M29" s="1">
         <v>5</v>
@@ -4529,34 +4528,34 @@
         <v>3.14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M30" s="1">
         <v>3</v>
@@ -4663,34 +4662,34 @@
         <v>2.98</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M31" s="1">
         <v>1</v>
@@ -4797,34 +4796,34 @@
         <v>3.2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M32" s="1">
         <v>4</v>
@@ -4931,34 +4930,34 @@
         <v>2.99</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M33" s="1">
         <v>4</v>
@@ -5065,34 +5064,34 @@
         <v>3.19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M34" s="1">
         <v>3</v>
@@ -5199,34 +5198,34 @@
         <v>3.1</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J35" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M35" s="1">
         <v>4</v>
@@ -5333,34 +5332,34 @@
         <v>3.07</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M36" s="1">
         <v>3</v>
@@ -5467,34 +5466,34 @@
         <v>3.4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J37" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M37" s="1">
         <v>4</v>
@@ -5601,34 +5600,34 @@
         <v>3.14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="J38" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M38" s="1">
         <v>4</v>
@@ -5735,34 +5734,34 @@
         <v>3.54</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M39" s="1">
         <v>3</v>
@@ -5869,34 +5868,34 @@
         <v>2.9</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M40" s="1">
         <v>5</v>
@@ -6003,34 +6002,34 @@
         <v>3.56</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M41" s="1">
         <v>4</v>
@@ -6137,34 +6136,34 @@
         <v>3.01</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M42" s="1">
         <v>3</v>
@@ -6271,34 +6270,34 @@
         <v>2.8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J43" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M43" s="1">
         <v>3</v>
@@ -6405,34 +6404,34 @@
         <v>2.93</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I44" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M44" s="1">
         <v>4</v>
@@ -6539,34 +6538,34 @@
         <v>1.79</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -6673,34 +6672,34 @@
         <v>2.76</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M46" s="1">
         <v>4</v>
@@ -6807,34 +6806,34 @@
         <v>3.33</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M47" s="1">
         <v>4</v>
@@ -6941,34 +6940,34 @@
         <v>3.12</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J48" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M48" s="1">
         <v>5</v>
@@ -7075,34 +7074,34 @@
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M49" s="1">
         <v>5</v>
@@ -7209,34 +7208,34 @@
         <v>3.02</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M50" s="1">
         <v>3</v>
@@ -7343,34 +7342,34 @@
         <v>3.29</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I51" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M51" s="1">
         <v>5</v>
@@ -7477,34 +7476,34 @@
         <v>3.2</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I52" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M52" s="1">
         <v>3</v>
@@ -7611,34 +7610,34 @@
         <v>2.14</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M53" s="1">
         <v>4</v>
@@ -7745,34 +7744,34 @@
         <v>3.36</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M54" s="1">
         <v>4</v>
@@ -7879,34 +7878,34 @@
         <v>2.8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L55" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M55" s="1">
         <v>4</v>
@@ -8013,34 +8012,34 @@
         <v>3.21</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M56" s="1">
         <v>3</v>
@@ -8147,34 +8146,34 @@
         <v>2.95</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I57" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M57" s="1">
         <v>5</v>
@@ -8281,34 +8280,34 @@
         <v>2.8</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M58" s="1">
         <v>5</v>
@@ -8415,34 +8414,34 @@
         <v>2.34</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M59" s="1">
         <v>5</v>
@@ -8549,34 +8548,34 @@
         <v>2.95</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I60" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M60" s="1">
         <v>5</v>
@@ -8683,34 +8682,34 @@
         <v>3.29</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H61" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J61" s="1" t="s">
+      <c r="K61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L61" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M61" s="1">
         <v>5</v>
@@ -8817,34 +8816,34 @@
         <v>3.14</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G62" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H62" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J62" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M62" s="1">
         <v>5</v>
@@ -8951,34 +8950,34 @@
         <v>2.95</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I63" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K63" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M63" s="1">
         <v>5</v>
@@ -9085,34 +9084,34 @@
         <v>2.76</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G64" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K64" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M64" s="1">
         <v>5</v>
@@ -9219,34 +9218,34 @@
         <v>3.05</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J65" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M65" s="1">
         <v>5</v>
@@ -9353,34 +9352,34 @@
         <v>3.1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G66" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J66" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M66" s="1">
         <v>4</v>
@@ -9487,34 +9486,34 @@
         <v>3.33</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K67" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M67" s="1">
         <v>5</v>
@@ -9621,34 +9620,34 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M68" s="1">
         <v>5</v>
@@ -9755,34 +9754,34 @@
         <v>3.43</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K69" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M69" s="1">
         <v>4</v>
@@ -9889,34 +9888,34 @@
         <v>2.65</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J70" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M70" s="1">
         <v>5</v>
@@ -10023,34 +10022,34 @@
         <v>3.02</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J71" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M71" s="1">
         <v>3</v>
@@ -10157,34 +10156,34 @@
         <v>2.76</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M72" s="1">
         <v>4</v>
@@ -10291,34 +10290,34 @@
         <v>3.24</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J73" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M73" s="1">
         <v>5</v>
@@ -10425,34 +10424,34 @@
         <v>3.45</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M74" s="1">
         <v>5</v>
@@ -10559,34 +10558,34 @@
         <v>2.1</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I75" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M75" s="1">
         <v>2</v>
@@ -10693,34 +10692,34 @@
         <v>2.79</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J76" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M76" s="1">
         <v>5</v>
@@ -10827,34 +10826,34 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I77" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M77" s="1">
         <v>5</v>
@@ -10961,34 +10960,34 @@
         <v>3.1</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G78" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L78" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M78" s="1">
         <v>4</v>
@@ -11095,34 +11094,34 @@
         <v>3.14</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J79" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M79" s="1">
         <v>5</v>
@@ -11229,34 +11228,34 @@
         <v>3.24</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M80" s="1">
         <v>4</v>
@@ -11363,34 +11362,34 @@
         <v>2.8</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M81" s="1">
         <v>3</v>
@@ -11497,34 +11496,34 @@
         <v>2.99</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H82" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I82" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I82" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="J82" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M82" s="1">
         <v>4</v>
@@ -11631,34 +11630,34 @@
         <v>3.43</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K83" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L83" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M83" s="1">
         <v>5</v>
@@ -11765,34 +11764,34 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J84" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M84" s="1">
         <v>5</v>
@@ -11899,34 +11898,34 @@
         <v>3.48</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G85" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J85" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M85" s="1">
         <v>5</v>
@@ -12033,34 +12032,34 @@
         <v>3.48</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="H86" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="J86" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M86" s="1">
         <v>3</v>
@@ -12167,34 +12166,34 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J87" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K87" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M87" s="1">
         <v>5</v>
@@ -12301,34 +12300,34 @@
         <v>3.14</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I88" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M88" s="1">
         <v>5</v>
@@ -12435,34 +12434,34 @@
         <v>2.29</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G89" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I89" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M89" s="1">
         <v>5</v>
@@ -12569,34 +12568,34 @@
         <v>2.63</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G90" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H90" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J90" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L90" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M90" s="1">
         <v>5</v>
@@ -12703,34 +12702,34 @@
         <v>2.76</v>
       </c>
       <c r="C91" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G91" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J91" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M91" s="1">
         <v>4</v>
@@ -12837,34 +12836,34 @@
         <v>3.07</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H92" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L92" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M92" s="1">
         <v>3</v>
@@ -12971,34 +12970,34 @@
         <v>3.55</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J93" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M93" s="1">
         <v>5</v>
@@ -13105,34 +13104,34 @@
         <v>3.1</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="F94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G94" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M94" s="1">
         <v>5</v>
@@ -13239,34 +13238,34 @@
         <v>2.98</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G95" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I95" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J95" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L95" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M95" s="1">
         <v>3</v>
@@ -13373,34 +13372,34 @@
         <v>3.38</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M96" s="1">
         <v>2</v>
@@ -13507,34 +13506,34 @@
         <v>2.72</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M97" s="1">
         <v>3</v>
@@ -13641,34 +13640,34 @@
         <v>3.22</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G98" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="H98" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="K98" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M98" s="1">
         <v>5</v>
@@ -13775,34 +13774,34 @@
         <v>3.11</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M99" s="1">
         <v>3</v>
@@ -13909,34 +13908,34 @@
         <v>3.2</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="J100" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L100" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M100" s="1">
         <v>3</v>
@@ -14043,34 +14042,34 @@
         <v>3</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H101" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K101" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M101" s="1">
         <v>5</v>
@@ -14177,34 +14176,34 @@
         <v>3.19</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M102" s="1">
         <v>5</v>
@@ -14311,34 +14310,34 @@
         <v>3</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J103" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M103" s="1">
         <v>4</v>
@@ -14445,34 +14444,34 @@
         <v>2.9</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H104" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M104" s="1">
         <v>5</v>
@@ -14579,34 +14578,34 @@
         <v>2.98</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G105" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J105" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M105" s="1">
         <v>5</v>
@@ -14713,34 +14712,34 @@
         <v>3.26</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I106" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J106" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J106" s="1" t="s">
+      <c r="K106" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L106" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M106" s="1">
         <v>5</v>
@@ -14847,34 +14846,34 @@
         <v>3.12</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G107" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J107" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M107" s="1">
         <v>4</v>
@@ -14981,34 +14980,34 @@
         <v>3.14</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H108" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I108" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M108" s="1">
         <v>1</v>
@@ -15115,34 +15114,34 @@
         <v>2.98</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G109" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J109" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M109" s="1">
         <v>5</v>
@@ -15249,34 +15248,34 @@
         <v>2.9</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I110" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K110" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M110" s="1">
         <v>4</v>
@@ -15383,34 +15382,34 @@
         <v>3.2</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M111" s="1">
         <v>4</v>
@@ -15517,34 +15516,34 @@
         <v>2.96</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M112" s="1">
         <v>5</v>
@@ -15651,34 +15650,34 @@
         <v>2.97</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="F113" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G113" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M113" s="1">
         <v>5</v>
@@ -15785,34 +15784,34 @@
         <v>2.8</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F114" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I114" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K114" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M114" s="1">
         <v>4</v>
@@ -15919,34 +15918,34 @@
         <v>3.45</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I115" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M115" s="1">
         <v>5</v>
@@ -16053,34 +16052,34 @@
         <v>3.03</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G116" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H116" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L116" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M116" s="1">
         <v>5</v>
@@ -16187,34 +16186,34 @@
         <v>2.9</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F117" s="1" t="s">
+      <c r="G117" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G117" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H117" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M117" s="1">
         <v>5</v>
@@ -16321,34 +16320,34 @@
         <v>2.8</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I118" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J118" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M118" s="1">
         <v>3</v>
@@ -16455,34 +16454,34 @@
         <v>3.34</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J119" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K119" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L119" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M119" s="1">
         <v>5</v>
@@ -16589,34 +16588,34 @@
         <v>2.93</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G120" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I120" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J120" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M120" s="1">
         <v>4</v>
@@ -16723,34 +16722,34 @@
         <v>3.25</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G121" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M121" s="1">
         <v>3</v>
@@ -16857,34 +16856,34 @@
         <v>3.57</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K122" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M122" s="1">
         <v>5</v>
@@ -16991,34 +16990,34 @@
         <v>3.32</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H123" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J123" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I123" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="K123" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M123" s="1">
         <v>5</v>
@@ -17125,34 +17124,34 @@
         <v>3.61</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J124" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K124" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L124" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M124" s="1">
         <v>4</v>
@@ -17259,34 +17258,34 @@
         <v>3.03</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I125" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M125" s="1">
         <v>4</v>
@@ -17393,34 +17392,34 @@
         <v>3.67</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J126" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K126" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L126" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M126" s="1">
         <v>3</v>
@@ -17527,34 +17526,34 @@
         <v>3</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H127" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J127" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I127" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K127" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M127" s="1">
         <v>5</v>
@@ -17661,34 +17660,34 @@
         <v>3.35</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H128" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I128" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J128" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M128" s="1">
         <v>4</v>
@@ -17795,34 +17794,34 @@
         <v>2.41</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M129" s="1">
         <v>5</v>
@@ -17929,34 +17928,34 @@
         <v>2.97</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G130" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I130" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H130" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J130" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M130" s="1">
         <v>4</v>
@@ -18063,34 +18062,34 @@
         <v>3.5</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I131" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J131" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K131" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L131" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M131" s="1">
         <v>5</v>
@@ -18197,34 +18196,34 @@
         <v>1.7</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G132" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I132" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J132" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M132" s="1">
         <v>5</v>
@@ -18331,34 +18330,34 @@
         <v>3.4</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M133" s="1">
         <v>5</v>
@@ -18465,34 +18464,34 @@
         <v>3</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H134" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J134" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I134" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J134" s="1" t="s">
+      <c r="K134" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K134" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L134" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M134" s="1">
         <v>4</v>
@@ -18599,34 +18598,34 @@
         <v>3.19</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G135" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J135" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M135" s="1">
         <v>4</v>
@@ -18733,34 +18732,34 @@
         <v>4.34</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M136" s="1">
         <v>5</v>
@@ -18867,34 +18866,34 @@
         <v>3.64</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G137" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J137" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M137" s="1">
         <v>5</v>
@@ -19001,34 +19000,34 @@
         <v>2.9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M138" s="1">
         <v>5</v>
@@ -19135,34 +19134,34 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G139" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I139" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H139" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J139" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M139" s="1">
         <v>5</v>
@@ -19269,34 +19268,34 @@
         <v>2.8</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G140" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H140" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J140" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M140" s="1">
         <v>3</v>
@@ -19403,34 +19402,34 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H141" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I141" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J141" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M141" s="1">
         <v>5</v>
@@ -19537,34 +19536,34 @@
         <v>3.59</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G142" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H142" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H142" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I142" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M142" s="1">
         <v>5</v>
@@ -19671,34 +19670,34 @@
         <v>2.58</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G143" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H143" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H143" s="1" t="s">
+      <c r="I143" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I143" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J143" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M143" s="1">
         <v>5</v>
@@ -19805,34 +19804,34 @@
         <v>2.94</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K144" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L144" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L144" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M144" s="1">
         <v>5</v>
@@ -19939,34 +19938,34 @@
         <v>3.22</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K145" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L145" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L145" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M145" s="1">
         <v>5</v>
@@ -20073,34 +20072,34 @@
         <v>2.81</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G146" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H146" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M146" s="1">
         <v>4</v>
@@ -20207,34 +20206,34 @@
         <v>2.9</v>
       </c>
       <c r="C147" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F147" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G147" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I147" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J147" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J147" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K147" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M147" s="1">
         <v>5</v>
@@ -20341,34 +20340,34 @@
         <v>3</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G148" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H148" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H148" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I148" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M148" s="1">
         <v>1</v>
@@ -20475,34 +20474,34 @@
         <v>2.14</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J149" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K149" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="L149" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M149" s="1">
         <v>2</v>
@@ -20609,34 +20608,34 @@
         <v>3.27</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J150" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K150" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K150" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="L150" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M150" s="1">
         <v>5</v>
@@ -20743,34 +20742,34 @@
         <v>3.58</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G151" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H151" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J151" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I151" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K151" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M151" s="1">
         <v>5</v>
@@ -20877,34 +20876,34 @@
         <v>3.6</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G152" s="1" t="s">
+      <c r="H152" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H152" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I152" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M152" s="1">
         <v>3</v>
@@ -21011,34 +21010,34 @@
         <v>2.8</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H153" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I153" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I153" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J153" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M153" s="1">
         <v>4</v>
@@ -21145,34 +21144,34 @@
         <v>3.1</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I154" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H154" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J154" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M154" s="1">
         <v>5</v>
@@ -21279,34 +21278,34 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H155" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I155" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M155" s="1">
         <v>5</v>
@@ -21413,34 +21412,34 @@
         <v>3.4</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H156" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J156" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I156" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K156" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M156" s="1">
         <v>5</v>
@@ -21547,34 +21546,34 @@
         <v>3.7</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D157" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="F157" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F157" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G157" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H157" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I157" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M157" s="1">
         <v>5</v>
@@ -21681,34 +21680,34 @@
         <v>3.03</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="F158" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G158" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J158" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L158" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L158" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M158" s="1">
         <v>3</v>
@@ -21815,34 +21814,34 @@
         <v>2.72</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M159" s="1">
         <v>5</v>
@@ -21949,34 +21948,34 @@
         <v>1.61</v>
       </c>
       <c r="C160" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D160" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E160" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F160" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G160" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H160" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J160" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M160" s="1">
         <v>5</v>
@@ -22083,34 +22082,34 @@
         <v>2.72</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D161" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F161" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G161" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H161" s="1" t="s">
+      <c r="I161" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I161" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J161" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M161" s="1">
         <v>5</v>
@@ -22217,34 +22216,34 @@
         <v>3.05</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I162" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J162" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="K162" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K162" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L162" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M162" s="1">
         <v>4</v>
@@ -22351,34 +22350,34 @@
         <v>1.7</v>
       </c>
       <c r="C163" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H163" s="1" t="s">
+      <c r="I163" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I163" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J163" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K163" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L163" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M163" s="1">
         <v>3</v>
@@ -22485,34 +22484,34 @@
         <v>2.6</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I164" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J164" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J164" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="K164" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M164" s="1">
         <v>5</v>
@@ -22619,34 +22618,34 @@
         <v>3.4</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D165" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E165" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F165" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H165" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J165" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I165" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J165" s="1" t="s">
+      <c r="K165" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K165" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="L165" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M165" s="1">
         <v>3</v>
@@ -22753,34 +22752,34 @@
         <v>2.9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I166" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H166" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J166" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M166" s="1">
         <v>3</v>
@@ -22887,34 +22886,34 @@
         <v>2.41</v>
       </c>
       <c r="C167" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I167" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F167" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="J167" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M167" s="1">
         <v>5</v>
@@ -23021,34 +23020,34 @@
         <v>3.31</v>
       </c>
       <c r="C168" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G168" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H168" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H168" s="1" t="s">
+      <c r="I168" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I168" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J168" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M168" s="1">
         <v>4</v>
@@ -23155,34 +23154,34 @@
         <v>3.34</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G169" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I169" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H169" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J169" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M169" s="1">
         <v>4</v>
@@ -23289,34 +23288,34 @@
         <v>3.25</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J170" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L170" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K170" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L170" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M170" s="1">
         <v>5</v>
@@ -23423,34 +23422,34 @@
         <v>2.06</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E171" s="1" t="s">
+      <c r="F171" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F171" s="1" t="s">
+      <c r="G171" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G171" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H171" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M171" s="1">
         <v>5</v>
@@ -23557,34 +23556,34 @@
         <v>2.8</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H172" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J172" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I172" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J172" s="1" t="s">
+      <c r="K172" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K172" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L172" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M172" s="1">
         <v>3</v>
@@ -23691,34 +23690,34 @@
         <v>2.5</v>
       </c>
       <c r="C173" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G173" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I173" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H173" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J173" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M173" s="1">
         <v>4</v>
@@ -23825,34 +23824,34 @@
         <v>2.81</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F174" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G174" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G174" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H174" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K174" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L174" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L174" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M174" s="1">
         <v>4</v>
@@ -23959,34 +23958,34 @@
         <v>2.38</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D175" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E175" s="1" t="s">
+      <c r="F175" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G175" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H175" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="I175" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M175" s="1">
         <v>5</v>
@@ -24093,34 +24092,34 @@
         <v>3.46</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I176" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H176" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J176" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M176" s="1">
         <v>5</v>
@@ -24227,34 +24226,34 @@
         <v>2.64</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M177" s="1">
         <v>5</v>
@@ -24361,34 +24360,34 @@
         <v>3.54</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M178" s="1">
         <v>5</v>
@@ -24495,34 +24494,34 @@
         <v>3.9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M179" s="1">
         <v>5</v>
@@ -24629,34 +24628,34 @@
         <v>2.9</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M180" s="1">
         <v>5</v>
@@ -24763,34 +24762,34 @@
         <v>3.8</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J181" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L181" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K181" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L181" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M181" s="1">
         <v>5</v>
@@ -24897,34 +24896,34 @@
         <v>3.22</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M182" s="1">
         <v>4</v>
@@ -25031,34 +25030,34 @@
         <v>2.57</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="F183" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F183" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G183" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M183" s="1">
         <v>3</v>
@@ -25165,34 +25164,34 @@
         <v>3.05</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G184" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H184" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H184" s="1" t="s">
+      <c r="I184" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I184" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J184" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M184" s="1">
         <v>3</v>
@@ -25299,34 +25298,34 @@
         <v>3.04</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G185" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H185" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H185" s="1" t="s">
+      <c r="I185" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I185" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J185" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L185" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K185" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="M185" s="1">
         <v>3</v>
@@ -25433,34 +25432,34 @@
         <v>3.17</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M186" s="1">
         <v>4</v>
@@ -25560,7 +25559,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR186" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AR186"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
